--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dd6a1203e1b71bc3/New folder/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="8_{5B4F4D9A-A209-4859-8430-BA5FE949862F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD84095C-C979-4EE2-ADE1-84BBD9A45BC2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB375141-8493-4D46-AA36-3F3662496C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,6 +18,15 @@
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -26,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -197,6 +206,18 @@
   </si>
   <si>
     <t>Today was the first day of college, I was feeling very tired because till date I had never attended so many classes in one day.</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Feeling good.</t>
   </si>
 </sst>
 </file>
@@ -977,7 +998,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A6" s="8">
         <v>46244</v>
       </c>
@@ -1024,26 +1045,50 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
+      <c r="A7" s="13">
+        <v>46245</v>
+      </c>
+      <c r="B7" s="14">
+        <v>360</v>
+      </c>
+      <c r="C7" s="14">
+        <v>45</v>
+      </c>
+      <c r="D7" s="14">
+        <v>200</v>
+      </c>
+      <c r="E7" s="14">
+        <v>30</v>
+      </c>
+      <c r="F7" s="14">
+        <v>200</v>
+      </c>
+      <c r="G7" s="14">
+        <v>4</v>
+      </c>
+      <c r="H7" s="14">
+        <v>200</v>
+      </c>
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+        <v>1035</v>
+      </c>
+      <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="17"/>
+        <v>405</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB375141-8493-4D46-AA36-3F3662496C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B025C3A-5C63-4E25-8B3B-01F0F01305CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -218,6 +218,15 @@
   </si>
   <si>
     <t>Feeling good.</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Today was simple day filled with work.</t>
   </si>
 </sst>
 </file>
@@ -1090,27 +1099,51 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+    <row r="8" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A8" s="13">
+        <v>46246</v>
+      </c>
+      <c r="B8" s="14">
+        <v>300</v>
+      </c>
+      <c r="C8" s="14">
+        <v>35</v>
+      </c>
+      <c r="D8" s="14">
+        <v>180</v>
+      </c>
+      <c r="E8" s="14">
+        <v>90</v>
+      </c>
+      <c r="F8" s="14">
+        <v>350</v>
+      </c>
+      <c r="G8" s="14">
+        <v>7</v>
+      </c>
+      <c r="H8" s="14">
+        <v>190</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>1145</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>295</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B025C3A-5C63-4E25-8B3B-01F0F01305CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1BE5DE7-A13D-45B5-B1F7-424398BB5A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -227,6 +227,9 @@
   </si>
   <si>
     <t>Today was simple day filled with work.</t>
+  </si>
+  <si>
+    <t>Normal day.</t>
   </si>
 </sst>
 </file>
@@ -1146,26 +1149,50 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46247</v>
+      </c>
+      <c r="B9" s="14">
+        <v>360</v>
+      </c>
+      <c r="C9" s="14">
+        <v>25</v>
+      </c>
+      <c r="D9" s="14">
+        <v>200</v>
+      </c>
+      <c r="E9" s="14">
+        <v>0</v>
+      </c>
+      <c r="F9" s="14">
+        <v>150</v>
+      </c>
+      <c r="G9" s="14">
+        <v>3</v>
+      </c>
+      <c r="H9" s="14">
+        <v>200</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>935</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>505</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1BE5DE7-A13D-45B5-B1F7-424398BB5A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45112ED3-3E2A-4E42-98FF-2BB6C73E9956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -230,6 +230,9 @@
   </si>
   <si>
     <t>Normal day.</t>
+  </si>
+  <si>
+    <t>I was really exhausted after taking 6 classes.</t>
   </si>
 </sst>
 </file>
@@ -1194,27 +1197,51 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+    <row r="10" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" s="13">
+        <v>46248</v>
+      </c>
+      <c r="B10" s="14">
+        <v>300</v>
+      </c>
+      <c r="C10" s="14">
+        <v>30</v>
+      </c>
+      <c r="D10" s="14">
+        <v>240</v>
+      </c>
+      <c r="E10" s="14">
+        <v>60</v>
+      </c>
+      <c r="F10" s="14">
+        <v>300</v>
+      </c>
+      <c r="G10" s="14">
+        <v>6</v>
+      </c>
+      <c r="H10" s="14">
+        <v>200</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45112ED3-3E2A-4E42-98FF-2BB6C73E9956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{794787BC-0D53-456D-9BA1-E9B25430951C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -233,6 +233,9 @@
   </si>
   <si>
     <t>I was really exhausted after taking 6 classes.</t>
+  </si>
+  <si>
+    <t>I am getting bored.</t>
   </si>
 </sst>
 </file>
@@ -1244,26 +1247,50 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46249</v>
+      </c>
+      <c r="B11" s="14">
+        <v>360</v>
+      </c>
+      <c r="C11" s="14">
+        <v>40</v>
+      </c>
+      <c r="D11" s="14">
+        <v>200</v>
+      </c>
+      <c r="E11" s="14">
+        <v>30</v>
+      </c>
+      <c r="F11" s="14">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14">
+        <v>240</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>570</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{794787BC-0D53-456D-9BA1-E9B25430951C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A5B4752-C3A8-42A1-86AC-16448BAC5C4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1293,26 +1293,50 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46250</v>
+      </c>
+      <c r="B12" s="14">
+        <v>600</v>
+      </c>
+      <c r="C12" s="14">
+        <v>20</v>
+      </c>
+      <c r="D12" s="14">
+        <v>120</v>
+      </c>
+      <c r="E12" s="14">
+        <v>30</v>
+      </c>
+      <c r="F12" s="14">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14">
+        <v>360</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A5B4752-C3A8-42A1-86AC-16448BAC5C4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85AF1096-129D-49EA-849C-6B97EE3EB296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1339,26 +1339,50 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46251</v>
+      </c>
+      <c r="B13" s="14">
+        <v>480</v>
+      </c>
+      <c r="C13" s="14">
+        <v>60</v>
+      </c>
+      <c r="D13" s="14">
+        <v>200</v>
+      </c>
+      <c r="E13" s="14">
+        <v>30</v>
+      </c>
+      <c r="F13" s="14">
+        <v>350</v>
+      </c>
+      <c r="G13" s="14">
+        <v>7</v>
+      </c>
+      <c r="H13" s="14">
+        <v>200</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>120</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85AF1096-129D-49EA-849C-6B97EE3EB296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE8C9752-1093-4613-91D9-B1904B544FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -236,6 +236,9 @@
   </si>
   <si>
     <t>I am getting bored.</t>
+  </si>
+  <si>
+    <t>I met with my mentor today, and it was great connecting with them.</t>
   </si>
 </sst>
 </file>
@@ -1385,26 +1388,50 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46252</v>
+      </c>
+      <c r="B14" s="14">
+        <v>300</v>
+      </c>
+      <c r="C14" s="14">
+        <v>30</v>
+      </c>
+      <c r="D14" s="14">
+        <v>240</v>
+      </c>
+      <c r="E14" s="14">
+        <v>120</v>
+      </c>
+      <c r="F14" s="14">
+        <v>200</v>
+      </c>
+      <c r="G14" s="14">
+        <v>4</v>
+      </c>
+      <c r="H14" s="14">
+        <v>200</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>350</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N14" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE8C9752-1093-4613-91D9-B1904B544FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A80F56-4336-4207-A0A8-BEEC7DC9E0E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -239,6 +239,9 @@
   </si>
   <si>
     <t>I met with my mentor today, and it was great connecting with them.</t>
+  </si>
+  <si>
+    <t>Lots of Classes.</t>
   </si>
 </sst>
 </file>
@@ -1434,26 +1437,50 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46253</v>
+      </c>
+      <c r="B15" s="14">
+        <v>300</v>
+      </c>
+      <c r="C15" s="14">
+        <v>60</v>
+      </c>
+      <c r="D15" s="14">
+        <v>200</v>
+      </c>
+      <c r="E15" s="14">
+        <v>150</v>
+      </c>
+      <c r="F15" s="14">
+        <v>350</v>
+      </c>
+      <c r="G15" s="14">
+        <v>7</v>
+      </c>
+      <c r="H15" s="14">
+        <v>300</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1360</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>80</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A80F56-4336-4207-A0A8-BEEC7DC9E0E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72694039-6847-479F-995A-DB22D8C581C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -242,6 +242,9 @@
   </si>
   <si>
     <t>Lots of Classes.</t>
+  </si>
+  <si>
+    <t>Normal Day.</t>
   </si>
 </sst>
 </file>
@@ -1483,26 +1486,50 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B16" s="14">
+        <v>300</v>
+      </c>
+      <c r="C16" s="14">
+        <v>45</v>
+      </c>
+      <c r="D16" s="14">
+        <v>240</v>
+      </c>
+      <c r="E16" s="14">
+        <v>120</v>
+      </c>
+      <c r="F16" s="14">
+        <v>100</v>
+      </c>
+      <c r="G16" s="14">
+        <v>2</v>
+      </c>
+      <c r="H16" s="14">
+        <v>300</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1105</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>335</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72694039-6847-479F-995A-DB22D8C581C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E392EE6-AE23-496B-951C-9B93551C2CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1532,26 +1532,50 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B17" s="14">
+        <v>250</v>
+      </c>
+      <c r="C17" s="14">
+        <v>60</v>
+      </c>
+      <c r="D17" s="14">
+        <v>200</v>
+      </c>
+      <c r="E17" s="14">
+        <v>120</v>
+      </c>
+      <c r="F17" s="14">
+        <v>250</v>
+      </c>
+      <c r="G17" s="14">
+        <v>5</v>
+      </c>
+      <c r="H17" s="14">
+        <v>360</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>200</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E392EE6-AE23-496B-951C-9B93551C2CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F25EB7C-C599-4E47-8DA3-3E8A018B4047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -245,6 +245,9 @@
   </si>
   <si>
     <t>Normal Day.</t>
+  </si>
+  <si>
+    <t>It's a normal day.</t>
   </si>
 </sst>
 </file>
@@ -1578,26 +1581,50 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B18" s="14">
+        <v>300</v>
+      </c>
+      <c r="C18" s="14">
+        <v>60</v>
+      </c>
+      <c r="D18" s="14">
+        <v>300</v>
+      </c>
+      <c r="E18" s="14">
+        <v>200</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>400</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>180</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F25EB7C-C599-4E47-8DA3-3E8A018B4047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{224A1290-18E8-4526-B50C-FC3B26FEED0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -248,6 +248,9 @@
   </si>
   <si>
     <t>It's a normal day.</t>
+  </si>
+  <si>
+    <t>Boring day.</t>
   </si>
 </sst>
 </file>
@@ -1627,26 +1630,50 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B19" s="14">
+        <v>600</v>
+      </c>
+      <c r="C19" s="14">
+        <v>45</v>
+      </c>
+      <c r="D19" s="14">
+        <v>400</v>
+      </c>
+      <c r="E19" s="14">
+        <v>60</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>300</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1405</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>35</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{224A1290-18E8-4526-B50C-FC3B26FEED0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{113B0343-EDF1-471D-8FB0-642370ED6EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1676,26 +1676,50 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B20" s="14">
+        <v>300</v>
+      </c>
+      <c r="C20" s="14">
+        <v>60</v>
+      </c>
+      <c r="D20" s="14">
+        <v>300</v>
+      </c>
+      <c r="E20" s="14">
+        <v>200</v>
+      </c>
+      <c r="F20" s="14">
+        <v>300</v>
+      </c>
+      <c r="G20" s="14">
+        <v>6</v>
+      </c>
+      <c r="H20" s="14">
+        <v>200</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1360</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>80</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{113B0343-EDF1-471D-8FB0-642370ED6EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D8CBC4-E59A-4E05-9E6B-83B05061E42D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1722,26 +1722,50 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B21" s="14">
+        <v>300</v>
+      </c>
+      <c r="C21" s="14">
+        <v>60</v>
+      </c>
+      <c r="D21" s="14">
+        <v>300</v>
+      </c>
+      <c r="E21" s="14">
+        <v>90</v>
+      </c>
+      <c r="F21" s="14">
+        <v>350</v>
+      </c>
+      <c r="G21" s="14">
+        <v>7</v>
+      </c>
+      <c r="H21" s="14">
+        <v>200</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>140</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D8CBC4-E59A-4E05-9E6B-83B05061E42D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F4FC55-B1A1-4366-9DA5-6AD14413F9A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1768,26 +1768,50 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B22" s="14">
+        <v>300</v>
+      </c>
+      <c r="C22" s="14">
+        <v>60</v>
+      </c>
+      <c r="D22" s="14">
+        <v>300</v>
+      </c>
+      <c r="E22" s="14">
+        <v>30</v>
+      </c>
+      <c r="F22" s="14">
+        <v>300</v>
+      </c>
+      <c r="G22" s="14">
+        <v>6</v>
+      </c>
+      <c r="H22" s="14">
+        <v>200</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>250</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F4FC55-B1A1-4366-9DA5-6AD14413F9A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D4CBE3-8E60-446C-AFBA-393A5C99962B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -251,6 +251,9 @@
   </si>
   <si>
     <t>Boring day.</t>
+  </si>
+  <si>
+    <t>Going to Innovation Lab and see all the inovations.</t>
   </si>
 </sst>
 </file>
@@ -1813,27 +1816,51 @@
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+    <row r="23" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A23" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B23" s="14">
+        <v>300</v>
+      </c>
+      <c r="C23" s="14">
+        <v>45</v>
+      </c>
+      <c r="D23" s="14">
+        <v>200</v>
+      </c>
+      <c r="E23" s="14">
+        <v>90</v>
+      </c>
+      <c r="F23" s="14">
+        <v>200</v>
+      </c>
+      <c r="G23" s="14">
+        <v>4</v>
+      </c>
+      <c r="H23" s="14">
+        <v>300</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1135</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>305</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D4CBE3-8E60-446C-AFBA-393A5C99962B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD18B8C5-00D6-4964-B999-A63B9070C3AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -254,6 +254,12 @@
   </si>
   <si>
     <t>Going to Innovation Lab and see all the inovations.</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Good day.</t>
   </si>
 </sst>
 </file>
@@ -1863,26 +1869,50 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B24" s="14">
+        <v>250</v>
+      </c>
+      <c r="C24" s="14">
+        <v>30</v>
+      </c>
+      <c r="D24" s="14">
+        <v>300</v>
+      </c>
+      <c r="E24" s="14">
+        <v>120</v>
+      </c>
+      <c r="F24" s="14">
+        <v>200</v>
+      </c>
+      <c r="G24" s="14">
+        <v>4</v>
+      </c>
+      <c r="H24" s="14">
+        <v>200</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>340</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD18B8C5-00D6-4964-B999-A63B9070C3AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA79C564-DEC5-47B9-B28E-2C740C78C8C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -260,6 +260,9 @@
   </si>
   <si>
     <t>Good day.</t>
+  </si>
+  <si>
+    <t>Very tired this day.</t>
   </si>
 </sst>
 </file>
@@ -1915,26 +1918,50 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B25" s="14">
+        <v>300</v>
+      </c>
+      <c r="C25" s="14">
+        <v>60</v>
+      </c>
+      <c r="D25" s="14">
+        <v>200</v>
+      </c>
+      <c r="E25" s="14">
+        <v>180</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>250</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA79C564-DEC5-47B9-B28E-2C740C78C8C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73759D7F-60A5-46E5-8754-E5DE56855ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t>Very tired this day.</t>
+  </si>
+  <si>
+    <t>Lots of activities doing today.</t>
   </si>
 </sst>
 </file>
@@ -1964,26 +1967,50 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B26" s="14">
+        <v>300</v>
+      </c>
+      <c r="C26" s="14">
+        <v>60</v>
+      </c>
+      <c r="D26" s="14">
+        <v>400</v>
+      </c>
+      <c r="E26" s="14">
+        <v>200</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14">
+        <v>250</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>230</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73759D7F-60A5-46E5-8754-E5DE56855ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FC765CE-E1D8-4C80-B935-1109CFAB1608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -266,6 +266,9 @@
   </si>
   <si>
     <t>Lots of activities doing today.</t>
+  </si>
+  <si>
+    <t>felling good.</t>
   </si>
 </sst>
 </file>
@@ -2013,26 +2016,50 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B27" s="14">
+        <v>250</v>
+      </c>
+      <c r="C27" s="14">
+        <v>45</v>
+      </c>
+      <c r="D27" s="14">
+        <v>350</v>
+      </c>
+      <c r="E27" s="14">
+        <v>200</v>
+      </c>
+      <c r="F27" s="14">
+        <v>300</v>
+      </c>
+      <c r="G27" s="14">
+        <v>6</v>
+      </c>
+      <c r="H27" s="14">
+        <v>200</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1345</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>95</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FC765CE-E1D8-4C80-B935-1109CFAB1608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11D7A4B7-6529-4678-BC60-628F10AFF9A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -269,6 +269,9 @@
   </si>
   <si>
     <t>felling good.</t>
+  </si>
+  <si>
+    <t>All thing are good.</t>
   </si>
 </sst>
 </file>
@@ -2062,26 +2065,50 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B28" s="14">
+        <v>200</v>
+      </c>
+      <c r="C28" s="14">
+        <v>60</v>
+      </c>
+      <c r="D28" s="14">
+        <v>300</v>
+      </c>
+      <c r="E28" s="14">
+        <v>200</v>
+      </c>
+      <c r="F28" s="14">
+        <v>350</v>
+      </c>
+      <c r="G28" s="14">
+        <v>7</v>
+      </c>
+      <c r="H28" s="14">
+        <v>200</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1310</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>130</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11D7A4B7-6529-4678-BC60-628F10AFF9A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86E0C7D7-7578-4548-8158-178807E443B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -272,6 +272,9 @@
   </si>
   <si>
     <t>All thing are good.</t>
+  </si>
+  <si>
+    <t>Today is very exhausted day.</t>
   </si>
 </sst>
 </file>
@@ -2066,7 +2069,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="13">
-        <v>46296</v>
+        <v>46266</v>
       </c>
       <c r="B28" s="14">
         <v>200</v>
@@ -2111,26 +2114,50 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B29" s="14">
+        <v>200</v>
+      </c>
+      <c r="C29" s="14">
+        <v>45</v>
+      </c>
+      <c r="D29" s="14">
+        <v>300</v>
+      </c>
+      <c r="E29" s="14">
+        <v>60</v>
+      </c>
+      <c r="F29" s="14">
+        <v>300</v>
+      </c>
+      <c r="G29" s="14">
+        <v>6</v>
+      </c>
+      <c r="H29" s="14">
+        <v>100</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1005</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>435</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86E0C7D7-7578-4548-8158-178807E443B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2D1FA5-3902-4C44-9FA7-C29E464F6AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2160,26 +2160,50 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B30" s="14">
+        <v>200</v>
+      </c>
+      <c r="C30" s="14">
+        <v>60</v>
+      </c>
+      <c r="D30" s="14">
+        <v>200</v>
+      </c>
+      <c r="E30" s="14">
+        <v>120</v>
+      </c>
+      <c r="F30" s="14">
+        <v>150</v>
+      </c>
+      <c r="G30" s="14">
+        <v>3</v>
+      </c>
+      <c r="H30" s="14">
+        <v>200</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="13"/>

--- a/12610764.xlsx
+++ b/12610764.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2D1FA5-3902-4C44-9FA7-C29E464F6AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8133D04-0F85-4070-B22B-F52F3638D0A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -275,6 +275,9 @@
   </si>
   <si>
     <t>Today is very exhausted day.</t>
+  </si>
+  <si>
+    <t>Today is intractive session,it is very  helpful.</t>
   </si>
 </sst>
 </file>
@@ -2161,7 +2164,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="13">
-        <v>46270</v>
+        <v>46268</v>
       </c>
       <c r="B30" s="14">
         <v>200</v>
@@ -2205,27 +2208,51 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+    <row r="31" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A31" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B31" s="14">
+        <v>250</v>
+      </c>
+      <c r="C31" s="14">
+        <v>120</v>
+      </c>
+      <c r="D31" s="14">
+        <v>180</v>
+      </c>
+      <c r="E31" s="14">
+        <v>60</v>
+      </c>
+      <c r="F31" s="14">
+        <v>250</v>
+      </c>
+      <c r="G31" s="14">
+        <v>5</v>
+      </c>
+      <c r="H31" s="14">
+        <v>200</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="13"/>
